--- a/artfynd/A 61109-2022 artfynd.xlsx
+++ b/artfynd/A 61109-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61109-2022 artfynd.xlsx
+++ b/artfynd/A 61109-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,440 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126522749</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrböle, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>663777</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7038219</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126522698</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrböle, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>663783</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7038221</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 planta i knopp</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126522843</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrböle, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>663786</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7038188</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126522470</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrböle, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>663779</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7038219</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 planta i knopp</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elisabet Söderlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61109-2022 artfynd.xlsx
+++ b/artfynd/A 61109-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77105985</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70703615</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115812218</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115812844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117978164</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120761195</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120778496</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522470</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522698</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522749</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,8 +1917,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>